--- a/baselines/BASELINE_v9_WC_GL_PR.xlsx
+++ b/baselines/BASELINE_v9_WC_GL_PR.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E91"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1376,16 +1376,16 @@
         <v>Reserves</v>
       </c>
       <c r="B58" t="str">
-        <v>Beginning Gross Reserve</v>
+        <v>Beginning Net Reserve</v>
       </c>
       <c r="C58">
-        <v>NaN</v>
+        <v>20238829</v>
       </c>
       <c r="D58">
-        <v>NaN</v>
+        <v>25175941</v>
       </c>
       <c r="E58">
-        <v>NaN</v>
+        <v>28083245</v>
       </c>
     </row>
     <row r="59">
@@ -1393,16 +1393,16 @@
         <v>Reserves</v>
       </c>
       <c r="B59" t="str">
-        <v>Current-Year Gross Reserve</v>
+        <v>Current-Year Net Reserve</v>
       </c>
       <c r="C59">
-        <v>NaN</v>
+        <v>12677534</v>
       </c>
       <c r="D59">
-        <v>NaN</v>
+        <v>12235712</v>
       </c>
       <c r="E59">
-        <v>NaN</v>
+        <v>10055208</v>
       </c>
     </row>
     <row r="60">
@@ -1410,16 +1410,16 @@
         <v>Reserves</v>
       </c>
       <c r="B60" t="str">
-        <v>Gross Paid Losses</v>
+        <v>Net Paid Losses</v>
       </c>
       <c r="C60">
-        <v>NaN</v>
+        <v>16599598</v>
       </c>
       <c r="D60">
-        <v>NaN</v>
+        <v>18043731</v>
       </c>
       <c r="E60">
-        <v>NaN</v>
+        <v>17818360</v>
       </c>
     </row>
     <row r="61">
@@ -1427,16 +1427,16 @@
         <v>Reserves</v>
       </c>
       <c r="B61" t="str">
-        <v>Ending Gross Reserve</v>
+        <v>Ending Net Reserve</v>
       </c>
       <c r="C61">
-        <v>NaN</v>
+        <v>25175941</v>
       </c>
       <c r="D61">
-        <v>NaN</v>
+        <v>28083245</v>
       </c>
       <c r="E61">
-        <v>NaN</v>
+        <v>27493020</v>
       </c>
     </row>
     <row r="62">
@@ -1444,16 +1444,16 @@
         <v>Reserves</v>
       </c>
       <c r="B62" t="str">
-        <v>Beginning RI Recoverable</v>
+        <v>Expected Net Unpaid Loss</v>
       </c>
       <c r="C62">
-        <v>NaN</v>
+        <v>25175941</v>
       </c>
       <c r="D62">
-        <v>NaN</v>
+        <v>28083245</v>
       </c>
       <c r="E62">
-        <v>NaN</v>
+        <v>27493020</v>
       </c>
     </row>
     <row r="63">
@@ -1461,16 +1461,16 @@
         <v>Reserves</v>
       </c>
       <c r="B63" t="str">
-        <v>Ending RI Recoverable</v>
+        <v>Indicated Net Reserve at Confidence</v>
       </c>
       <c r="C63">
-        <v>NaN</v>
+        <v>33886817</v>
       </c>
       <c r="D63">
-        <v>NaN</v>
+        <v>37800048</v>
       </c>
       <c r="E63">
-        <v>NaN</v>
+        <v>37005605</v>
       </c>
     </row>
     <row r="64">
@@ -1478,50 +1478,50 @@
         <v>Reserves</v>
       </c>
       <c r="B64" t="str">
-        <v>Expected Net Unpaid Loss</v>
+        <v>Reserve Risk Margin Needed</v>
       </c>
       <c r="C64">
-        <v>25175941</v>
+        <v>23942320</v>
       </c>
       <c r="D64">
-        <v>28083245</v>
+        <v>26707166</v>
       </c>
       <c r="E64">
-        <v>27493020</v>
+        <v>26145862</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Reserves</v>
+        <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B65" t="str">
-        <v>Indicated Net Reserve at Confidence</v>
+        <v>Beginning Cash</v>
       </c>
       <c r="C65">
-        <v>33886817</v>
+        <v>5447649</v>
       </c>
       <c r="D65">
-        <v>37800048</v>
+        <v>6019061</v>
       </c>
       <c r="E65">
-        <v>37005605</v>
+        <v>6355360</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Reserves</v>
+        <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B66" t="str">
-        <v>Reserve Risk Margin Needed</v>
+        <v>Ending Cash</v>
       </c>
       <c r="C66">
-        <v>23942320</v>
+        <v>6019061</v>
       </c>
       <c r="D66">
-        <v>26707166</v>
+        <v>6355360</v>
       </c>
       <c r="E66">
-        <v>26145862</v>
+        <v>6659079</v>
       </c>
     </row>
     <row r="67">
@@ -1529,16 +1529,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B67" t="str">
-        <v>Beginning Cash</v>
+        <v>Beginning Investments</v>
       </c>
       <c r="C67">
-        <v>5447649</v>
+        <v>49873134</v>
       </c>
       <c r="D67">
-        <v>6019061</v>
+        <v>59201980</v>
       </c>
       <c r="E67">
-        <v>6355360</v>
+        <v>75316826</v>
       </c>
     </row>
     <row r="68">
@@ -1546,16 +1546,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B68" t="str">
-        <v>Ending Cash</v>
+        <v>Ending Investments</v>
       </c>
       <c r="C68">
-        <v>6019061</v>
+        <v>59201980</v>
       </c>
       <c r="D68">
-        <v>6355360</v>
+        <v>75316826</v>
       </c>
       <c r="E68">
-        <v>6659079</v>
+        <v>91391339</v>
       </c>
     </row>
     <row r="69">
@@ -1563,16 +1563,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B69" t="str">
-        <v>Beginning Investments</v>
+        <v>Other Assets</v>
       </c>
       <c r="C69">
-        <v>49873134</v>
+        <v>693194</v>
       </c>
       <c r="D69">
-        <v>59201980</v>
+        <v>693194</v>
       </c>
       <c r="E69">
-        <v>75316826</v>
+        <v>693194</v>
       </c>
     </row>
     <row r="70">
@@ -1580,16 +1580,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B70" t="str">
-        <v>Ending Investments</v>
+        <v>Total Assets</v>
       </c>
       <c r="C70">
-        <v>59201980</v>
+        <v>65914236</v>
       </c>
       <c r="D70">
-        <v>75316826</v>
+        <v>82365380</v>
       </c>
       <c r="E70">
-        <v>91391339</v>
+        <v>98743612</v>
       </c>
     </row>
     <row r="71">
@@ -1597,16 +1597,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B71" t="str">
-        <v>Other Assets</v>
+        <v>Unearned Premium</v>
       </c>
       <c r="C71">
-        <v>693194</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>693194</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>693194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1614,16 +1614,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B72" t="str">
-        <v>Total Assets</v>
+        <v>Other Liabilities</v>
       </c>
       <c r="C72">
-        <v>65914236</v>
+        <v>733460</v>
       </c>
       <c r="D72">
-        <v>82365380</v>
+        <v>733460</v>
       </c>
       <c r="E72">
-        <v>98743612</v>
+        <v>733460</v>
       </c>
     </row>
     <row r="73">
@@ -1631,16 +1631,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B73" t="str">
-        <v>Unearned Premium</v>
+        <v>Total Liabilities</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>25909401</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>28816706</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>28226480</v>
       </c>
     </row>
     <row r="74">
@@ -1648,16 +1648,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B74" t="str">
-        <v>Other Liabilities</v>
+        <v>Beginning Surplus</v>
       </c>
       <c r="C74">
-        <v>733460</v>
+        <v>35041688</v>
       </c>
       <c r="D74">
-        <v>733460</v>
+        <v>40004834</v>
       </c>
       <c r="E74">
-        <v>733460</v>
+        <v>53548675</v>
       </c>
     </row>
     <row r="75">
@@ -1665,16 +1665,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B75" t="str">
-        <v>Total Liabilities</v>
+        <v>Surplus from Income</v>
       </c>
       <c r="C75">
-        <v>25909401</v>
+        <v>40004834</v>
       </c>
       <c r="D75">
-        <v>28816706</v>
+        <v>53548675</v>
       </c>
       <c r="E75">
-        <v>28226480</v>
+        <v>70517132</v>
       </c>
     </row>
     <row r="76">
@@ -1682,16 +1682,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B76" t="str">
-        <v>Beginning Surplus</v>
+        <v>Ending Surplus</v>
       </c>
       <c r="C76">
-        <v>35041688</v>
+        <v>40004834</v>
       </c>
       <c r="D76">
-        <v>40004834</v>
+        <v>53548675</v>
       </c>
       <c r="E76">
-        <v>53548675</v>
+        <v>70517132</v>
       </c>
     </row>
     <row r="77">
@@ -1699,41 +1699,41 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B77" t="str">
-        <v>Surplus from Income</v>
+        <v>Surplus Tie-Out Difference</v>
       </c>
       <c r="C77">
-        <v>40004834</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>53548675</v>
+        <v>0</v>
       </c>
       <c r="E77">
-        <v>70517132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Balance Sheet and Surplus</v>
+        <v>Inter-Line Loan</v>
       </c>
       <c r="B78" t="str">
-        <v>Ending Surplus</v>
+        <v>Loan Originated This Year</v>
       </c>
       <c r="C78">
-        <v>40004834</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>53548675</v>
+        <v>0</v>
       </c>
       <c r="E78">
-        <v>70517132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Balance Sheet and Surplus</v>
+        <v>Inter-Line Loan</v>
       </c>
       <c r="B79" t="str">
-        <v>Surplus Tie-Out Difference</v>
+        <v>Loan Interest Accrued</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -1750,7 +1750,7 @@
         <v>Inter-Line Loan</v>
       </c>
       <c r="B80" t="str">
-        <v>Loan Originated This Year</v>
+        <v>Loan Repayment Applied</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -1767,7 +1767,7 @@
         <v>Inter-Line Loan</v>
       </c>
       <c r="B81" t="str">
-        <v>Loan Interest Accrued</v>
+        <v>Outstanding Loan Balance</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -1781,36 +1781,36 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Inter-Line Loan</v>
+        <v>Ratios and Capital</v>
       </c>
       <c r="B82" t="str">
-        <v>Loan Repayment Applied</v>
+        <v>Expected Loss Ratio</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>0.6684491978609625</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>0.6684491978609625</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>0.6684491978609626</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Inter-Line Loan</v>
+        <v>Ratios and Capital</v>
       </c>
       <c r="B83" t="str">
-        <v>Outstanding Loan Balance</v>
+        <v>Expected Expense Ratio</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>0.33155080213903754</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>0.33155080213903754</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>0.3315508021390374</v>
       </c>
     </row>
     <row r="84">
@@ -1818,16 +1818,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B84" t="str">
-        <v>Expected Loss Ratio</v>
+        <v>Expected Combined Ratio</v>
       </c>
       <c r="C84">
-        <v>0.6684491978609625</v>
+        <v>1</v>
       </c>
       <c r="D84">
-        <v>0.6684491978609625</v>
+        <v>1</v>
       </c>
       <c r="E84">
-        <v>0.6684491978609626</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -1835,16 +1835,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B85" t="str">
-        <v>Expected Expense Ratio</v>
+        <v>Actual Loss Ratio</v>
       </c>
       <c r="C85">
-        <v>0.33155080213903754</v>
+        <v>0.5367126802497094</v>
       </c>
       <c r="D85">
-        <v>0.33155080213903754</v>
+        <v>0.4944889433941472</v>
       </c>
       <c r="E85">
-        <v>0.3315508021390374</v>
+        <v>0.3880746887065281</v>
       </c>
     </row>
     <row r="86">
@@ -1852,16 +1852,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B86" t="str">
-        <v>Expected Combined Ratio</v>
+        <v>Actual Expense Ratio</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>0.3294687740591458</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0.3294687740591458</v>
       </c>
       <c r="E86">
-        <v>1</v>
+        <v>0.3294687740591459</v>
       </c>
     </row>
     <row r="87">
@@ -1869,16 +1869,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B87" t="str">
-        <v>Actual Loss Ratio</v>
+        <v>Actual Combined Ratio</v>
       </c>
       <c r="C87">
-        <v>0.5367126802497094</v>
+        <v>0.8661814543088553</v>
       </c>
       <c r="D87">
-        <v>0.4944889433941472</v>
+        <v>0.823957717453293</v>
       </c>
       <c r="E87">
-        <v>0.3880746887065281</v>
+        <v>0.717543462765674</v>
       </c>
     </row>
     <row r="88">
@@ -1886,16 +1886,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B88" t="str">
-        <v>Actual Expense Ratio</v>
+        <v>Surplus</v>
       </c>
       <c r="C88">
-        <v>0.3294687740591458</v>
+        <v>40004834</v>
       </c>
       <c r="D88">
-        <v>0.3294687740591458</v>
+        <v>53548675</v>
       </c>
       <c r="E88">
-        <v>0.3294687740591459</v>
+        <v>70517132</v>
       </c>
     </row>
     <row r="89">
@@ -1903,16 +1903,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B89" t="str">
-        <v>Actual Combined Ratio</v>
+        <v>Excess Available Surplus</v>
       </c>
       <c r="C89">
-        <v>0.8661814543088553</v>
+        <v>16062514</v>
       </c>
       <c r="D89">
-        <v>0.823957717453293</v>
+        <v>26841508</v>
       </c>
       <c r="E89">
-        <v>0.717543462765674</v>
+        <v>44371270</v>
       </c>
     </row>
     <row r="90">
@@ -1920,16 +1920,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B90" t="str">
-        <v>Surplus</v>
+        <v>Excess Capital Ratio</v>
       </c>
       <c r="C90">
-        <v>40004834</v>
+        <v>0.6708837791314776</v>
       </c>
       <c r="D90">
-        <v>53548675</v>
+        <v>1.00503017014399</v>
       </c>
       <c r="E90">
-        <v>70517132</v>
+        <v>1.697066636989923</v>
       </c>
     </row>
     <row r="91">
@@ -1937,62 +1937,28 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B91" t="str">
-        <v>Excess Available Surplus</v>
-      </c>
-      <c r="C91">
-        <v>16062514</v>
-      </c>
-      <c r="D91">
-        <v>26841508</v>
-      </c>
-      <c r="E91">
-        <v>44371270</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B92" t="str">
-        <v>Excess Capital Ratio</v>
-      </c>
-      <c r="C92">
-        <v>0.6708837791314776</v>
-      </c>
-      <c r="D92">
-        <v>1.00503017014399</v>
-      </c>
-      <c r="E92">
-        <v>1.697066636989923</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B93" t="str">
         <v>Excess Capital Status</v>
       </c>
-      <c r="C93" t="str">
+      <c r="C91" t="str">
         <v>Strong</v>
       </c>
-      <c r="D93" t="str">
+      <c r="D91" t="str">
         <v>Strong</v>
       </c>
-      <c r="E93" t="str">
+      <c r="E91" t="str">
         <v>Strong</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E93"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E91"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E85"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2866,16 +2832,16 @@
         <v>Reserves</v>
       </c>
       <c r="B52" t="str">
-        <v>Beginning Gross Reserve</v>
+        <v>Beginning Net Reserve</v>
       </c>
       <c r="C52">
-        <v>NaN</v>
+        <v>7651348</v>
       </c>
       <c r="D52">
-        <v>NaN</v>
+        <v>8353677</v>
       </c>
       <c r="E52">
-        <v>NaN</v>
+        <v>9230462</v>
       </c>
     </row>
     <row r="53">
@@ -2883,16 +2849,16 @@
         <v>Reserves</v>
       </c>
       <c r="B53" t="str">
-        <v>Current-Year Gross Reserve</v>
+        <v>Current-Year Net Reserve</v>
       </c>
       <c r="C53">
-        <v>NaN</v>
+        <v>3348984</v>
       </c>
       <c r="D53">
-        <v>NaN</v>
+        <v>3573605</v>
       </c>
       <c r="E53">
-        <v>NaN</v>
+        <v>4410895</v>
       </c>
     </row>
     <row r="54">
@@ -2900,16 +2866,16 @@
         <v>Reserves</v>
       </c>
       <c r="B54" t="str">
-        <v>Gross Paid Losses</v>
+        <v>Net Paid Losses</v>
       </c>
       <c r="C54">
-        <v>NaN</v>
+        <v>4927491</v>
       </c>
       <c r="D54">
-        <v>NaN</v>
+        <v>5428403</v>
       </c>
       <c r="E54">
-        <v>NaN</v>
+        <v>6218237</v>
       </c>
     </row>
     <row r="55">
@@ -2917,16 +2883,16 @@
         <v>Reserves</v>
       </c>
       <c r="B55" t="str">
-        <v>Ending Gross Reserve</v>
+        <v>Ending Net Reserve</v>
       </c>
       <c r="C55">
-        <v>NaN</v>
+        <v>8353677</v>
       </c>
       <c r="D55">
-        <v>NaN</v>
+        <v>9230462</v>
       </c>
       <c r="E55">
-        <v>NaN</v>
+        <v>10497942</v>
       </c>
     </row>
     <row r="56">
@@ -2934,16 +2900,16 @@
         <v>Reserves</v>
       </c>
       <c r="B56" t="str">
-        <v>Beginning RI Recoverable</v>
+        <v>Expected Net Unpaid Loss</v>
       </c>
       <c r="C56">
-        <v>NaN</v>
+        <v>8353677</v>
       </c>
       <c r="D56">
-        <v>NaN</v>
+        <v>9230462</v>
       </c>
       <c r="E56">
-        <v>NaN</v>
+        <v>10497942</v>
       </c>
     </row>
     <row r="57">
@@ -2951,16 +2917,16 @@
         <v>Reserves</v>
       </c>
       <c r="B57" t="str">
-        <v>Ending RI Recoverable</v>
+        <v>Indicated Net Reserve at Confidence</v>
       </c>
       <c r="C57">
-        <v>NaN</v>
+        <v>11244050</v>
       </c>
       <c r="D57">
-        <v>NaN</v>
+        <v>12424202</v>
       </c>
       <c r="E57">
-        <v>NaN</v>
+        <v>14130229</v>
       </c>
     </row>
     <row r="58">
@@ -2968,50 +2934,50 @@
         <v>Reserves</v>
       </c>
       <c r="B58" t="str">
-        <v>Expected Net Unpaid Loss</v>
+        <v>Reserve Risk Margin Needed</v>
       </c>
       <c r="C58">
-        <v>8353677</v>
+        <v>7944347</v>
       </c>
       <c r="D58">
-        <v>9230462</v>
+        <v>8778170</v>
       </c>
       <c r="E58">
-        <v>10497942</v>
+        <v>9983542</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Reserves</v>
+        <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B59" t="str">
-        <v>Indicated Net Reserve at Confidence</v>
+        <v>Beginning Cash</v>
       </c>
       <c r="C59">
-        <v>11244050</v>
+        <v>1651674</v>
       </c>
       <c r="D59">
-        <v>12424202</v>
+        <v>1771577</v>
       </c>
       <c r="E59">
-        <v>14130229</v>
+        <v>1758251</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Reserves</v>
+        <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B60" t="str">
-        <v>Reserve Risk Margin Needed</v>
+        <v>Ending Cash</v>
       </c>
       <c r="C60">
-        <v>7944347</v>
+        <v>1771934</v>
       </c>
       <c r="D60">
-        <v>8778170</v>
+        <v>1758963</v>
       </c>
       <c r="E60">
-        <v>9983542</v>
+        <v>1974558</v>
       </c>
     </row>
     <row r="61">
@@ -3019,16 +2985,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B61" t="str">
-        <v>Beginning Cash</v>
+        <v>Beginning Investments</v>
       </c>
       <c r="C61">
-        <v>1651674</v>
+        <v>18597505</v>
       </c>
       <c r="D61">
-        <v>1771577</v>
+        <v>21319049</v>
       </c>
       <c r="E61">
-        <v>1758251</v>
+        <v>25957475</v>
       </c>
     </row>
     <row r="62">
@@ -3036,16 +3002,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B62" t="str">
-        <v>Ending Cash</v>
+        <v>Ending Investments</v>
       </c>
       <c r="C62">
-        <v>1771934</v>
+        <v>21319049</v>
       </c>
       <c r="D62">
-        <v>1758963</v>
+        <v>25957475</v>
       </c>
       <c r="E62">
-        <v>1974558</v>
+        <v>29876085</v>
       </c>
     </row>
     <row r="63">
@@ -3053,16 +3019,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B63" t="str">
-        <v>Beginning Investments</v>
+        <v>Other Assets</v>
       </c>
       <c r="C63">
-        <v>18597505</v>
+        <v>210170</v>
       </c>
       <c r="D63">
-        <v>21319049</v>
+        <v>204026</v>
       </c>
       <c r="E63">
-        <v>25957475</v>
+        <v>191777</v>
       </c>
     </row>
     <row r="64">
@@ -3070,16 +3036,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B64" t="str">
-        <v>Ending Investments</v>
+        <v>Total Assets</v>
       </c>
       <c r="C64">
-        <v>21319049</v>
+        <v>23301152</v>
       </c>
       <c r="D64">
-        <v>25957475</v>
+        <v>27920464</v>
       </c>
       <c r="E64">
-        <v>29876085</v>
+        <v>32042419</v>
       </c>
     </row>
     <row r="65">
@@ -3087,16 +3053,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B65" t="str">
-        <v>Other Assets</v>
+        <v>Unearned Premium</v>
       </c>
       <c r="C65">
-        <v>210170</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>204026</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>191777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -3104,16 +3070,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B66" t="str">
-        <v>Total Assets</v>
+        <v>Other Liabilities</v>
       </c>
       <c r="C66">
-        <v>23301152</v>
+        <v>222378</v>
       </c>
       <c r="D66">
-        <v>27920464</v>
+        <v>215878</v>
       </c>
       <c r="E66">
-        <v>32042419</v>
+        <v>202917</v>
       </c>
     </row>
     <row r="67">
@@ -3121,16 +3087,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B67" t="str">
-        <v>Unearned Premium</v>
+        <v>Total Liabilities</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>8576055</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>9446340</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>10700858</v>
       </c>
     </row>
     <row r="68">
@@ -3138,16 +3104,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B68" t="str">
-        <v>Other Liabilities</v>
+        <v>Beginning Surplus</v>
       </c>
       <c r="C68">
-        <v>222378</v>
+        <v>12585622</v>
       </c>
       <c r="D68">
-        <v>215878</v>
+        <v>14725097</v>
       </c>
       <c r="E68">
-        <v>202917</v>
+        <v>18474124</v>
       </c>
     </row>
     <row r="69">
@@ -3155,16 +3121,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B69" t="str">
-        <v>Total Liabilities</v>
+        <v>Surplus from Income</v>
       </c>
       <c r="C69">
-        <v>8576055</v>
+        <v>14725097</v>
       </c>
       <c r="D69">
-        <v>9446340</v>
+        <v>18474124</v>
       </c>
       <c r="E69">
-        <v>10700858</v>
+        <v>21341561</v>
       </c>
     </row>
     <row r="70">
@@ -3172,16 +3138,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B70" t="str">
-        <v>Beginning Surplus</v>
+        <v>Ending Surplus</v>
       </c>
       <c r="C70">
-        <v>12585622</v>
+        <v>14725097</v>
       </c>
       <c r="D70">
-        <v>14725097</v>
+        <v>18474124</v>
       </c>
       <c r="E70">
-        <v>18474124</v>
+        <v>21341561</v>
       </c>
     </row>
     <row r="71">
@@ -3189,41 +3155,41 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B71" t="str">
-        <v>Surplus from Income</v>
+        <v>Surplus Tie-Out Difference</v>
       </c>
       <c r="C71">
-        <v>14725097</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>18474124</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>21341561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Balance Sheet and Surplus</v>
+        <v>Inter-Line Loan</v>
       </c>
       <c r="B72" t="str">
-        <v>Ending Surplus</v>
+        <v>Loan Originated This Year</v>
       </c>
       <c r="C72">
-        <v>14725097</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>18474124</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>21341561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Balance Sheet and Surplus</v>
+        <v>Inter-Line Loan</v>
       </c>
       <c r="B73" t="str">
-        <v>Surplus Tie-Out Difference</v>
+        <v>Loan Interest Accrued</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3240,7 +3206,7 @@
         <v>Inter-Line Loan</v>
       </c>
       <c r="B74" t="str">
-        <v>Loan Originated This Year</v>
+        <v>Loan Repayment Applied</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -3257,7 +3223,7 @@
         <v>Inter-Line Loan</v>
       </c>
       <c r="B75" t="str">
-        <v>Loan Interest Accrued</v>
+        <v>Outstanding Loan Balance</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -3271,36 +3237,36 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Inter-Line Loan</v>
+        <v>Ratios and Capital</v>
       </c>
       <c r="B76" t="str">
-        <v>Loan Repayment Applied</v>
+        <v>Expected Loss Ratio</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>0.6684491978609624</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>0.6684491978609625</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>0.6684491978609626</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Inter-Line Loan</v>
+        <v>Ratios and Capital</v>
       </c>
       <c r="B77" t="str">
-        <v>Outstanding Loan Balance</v>
+        <v>Expected Expense Ratio</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>0.33155080213903765</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>0.33155080213903754</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>0.3315508021390374</v>
       </c>
     </row>
     <row r="78">
@@ -3308,16 +3274,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B78" t="str">
-        <v>Expected Loss Ratio</v>
+        <v>Expected Combined Ratio</v>
       </c>
       <c r="C78">
-        <v>0.6684491978609624</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>0.6684491978609625</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>0.6684491978609626</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -3325,16 +3291,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B79" t="str">
-        <v>Expected Expense Ratio</v>
+        <v>Actual Loss Ratio</v>
       </c>
       <c r="C79">
-        <v>0.33155080213903765</v>
+        <v>0.47658261895766835</v>
       </c>
       <c r="D79">
-        <v>0.33155080213903754</v>
+        <v>0.5376908072671455</v>
       </c>
       <c r="E79">
-        <v>0.3315508021390374</v>
+        <v>0.5686627663861891</v>
       </c>
     </row>
     <row r="80">
@@ -3342,16 +3308,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B80" t="str">
-        <v>Expected Combined Ratio</v>
+        <v>Actual Expense Ratio</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>0.3294687740591458</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0.3294687740591458</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>0.32946877405914593</v>
       </c>
     </row>
     <row r="81">
@@ -3359,16 +3325,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B81" t="str">
-        <v>Actual Loss Ratio</v>
+        <v>Actual Combined Ratio</v>
       </c>
       <c r="C81">
-        <v>0.47658261895766835</v>
+        <v>0.8060513930168142</v>
       </c>
       <c r="D81">
-        <v>0.5376908072671455</v>
+        <v>0.8671595813262913</v>
       </c>
       <c r="E81">
-        <v>0.5686627663861891</v>
+        <v>0.8981315404453349</v>
       </c>
     </row>
     <row r="82">
@@ -3376,16 +3342,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B82" t="str">
-        <v>Actual Expense Ratio</v>
+        <v>Surplus</v>
       </c>
       <c r="C82">
-        <v>0.3294687740591458</v>
+        <v>14725097</v>
       </c>
       <c r="D82">
-        <v>0.3294687740591458</v>
+        <v>18474124</v>
       </c>
       <c r="E82">
-        <v>0.32946877405914593</v>
+        <v>21341561</v>
       </c>
     </row>
     <row r="83">
@@ -3393,16 +3359,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B83" t="str">
-        <v>Actual Combined Ratio</v>
+        <v>Excess Available Surplus</v>
       </c>
       <c r="C83">
-        <v>0.8060513930168142</v>
+        <v>6780750</v>
       </c>
       <c r="D83">
-        <v>0.8671595813262913</v>
+        <v>9695955</v>
       </c>
       <c r="E83">
-        <v>0.8981315404453349</v>
+        <v>11358018</v>
       </c>
     </row>
     <row r="84">
@@ -3410,16 +3376,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B84" t="str">
-        <v>Surplus</v>
+        <v>Excess Capital Ratio</v>
       </c>
       <c r="C84">
-        <v>14725097</v>
+        <v>0.8535313651626405</v>
       </c>
       <c r="D84">
-        <v>18474124</v>
+        <v>1.1045530901377665</v>
       </c>
       <c r="E84">
-        <v>21341561</v>
+        <v>1.1376741562175845</v>
       </c>
     </row>
     <row r="85">
@@ -3427,62 +3393,28 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B85" t="str">
-        <v>Excess Available Surplus</v>
-      </c>
-      <c r="C85">
-        <v>6780750</v>
-      </c>
-      <c r="D85">
-        <v>9695955</v>
-      </c>
-      <c r="E85">
-        <v>11358018</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Excess Capital Ratio</v>
-      </c>
-      <c r="C86">
-        <v>0.8535313651626405</v>
-      </c>
-      <c r="D86">
-        <v>1.1045530901377665</v>
-      </c>
-      <c r="E86">
-        <v>1.1376741562175845</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B87" t="str">
         <v>Excess Capital Status</v>
       </c>
-      <c r="C87" t="str">
+      <c r="C85" t="str">
         <v>Strong</v>
       </c>
-      <c r="D87" t="str">
+      <c r="D85" t="str">
         <v>Strong</v>
       </c>
-      <c r="E87" t="str">
+      <c r="E85" t="str">
         <v>Strong</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E85"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E85"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4356,16 +4288,16 @@
         <v>Reserves</v>
       </c>
       <c r="B52" t="str">
-        <v>Beginning Gross Reserve</v>
+        <v>Beginning Net Reserve</v>
       </c>
       <c r="C52">
-        <v>NaN</v>
+        <v>9447719</v>
       </c>
       <c r="D52">
-        <v>NaN</v>
+        <v>13940218</v>
       </c>
       <c r="E52">
-        <v>NaN</v>
+        <v>15243348</v>
       </c>
     </row>
     <row r="53">
@@ -4373,16 +4305,16 @@
         <v>Reserves</v>
       </c>
       <c r="B53" t="str">
-        <v>Current-Year Gross Reserve</v>
+        <v>Current-Year Net Reserve</v>
       </c>
       <c r="C53">
-        <v>NaN</v>
+        <v>7521818</v>
       </c>
       <c r="D53">
-        <v>NaN</v>
+        <v>6078926</v>
       </c>
       <c r="E53">
-        <v>NaN</v>
+        <v>3560035</v>
       </c>
     </row>
     <row r="54">
@@ -4390,16 +4322,16 @@
         <v>Reserves</v>
       </c>
       <c r="B54" t="str">
-        <v>Gross Paid Losses</v>
+        <v>Net Paid Losses</v>
       </c>
       <c r="C54">
-        <v>NaN</v>
+        <v>8470607</v>
       </c>
       <c r="D54">
-        <v>NaN</v>
+        <v>8987306</v>
       </c>
       <c r="E54">
-        <v>NaN</v>
+        <v>7780811</v>
       </c>
     </row>
     <row r="55">
@@ -4407,16 +4339,16 @@
         <v>Reserves</v>
       </c>
       <c r="B55" t="str">
-        <v>Ending Gross Reserve</v>
+        <v>Ending Net Reserve</v>
       </c>
       <c r="C55">
-        <v>NaN</v>
+        <v>13940218</v>
       </c>
       <c r="D55">
-        <v>NaN</v>
+        <v>15243348</v>
       </c>
       <c r="E55">
-        <v>NaN</v>
+        <v>13602450</v>
       </c>
     </row>
     <row r="56">
@@ -4424,16 +4356,16 @@
         <v>Reserves</v>
       </c>
       <c r="B56" t="str">
-        <v>Beginning RI Recoverable</v>
+        <v>Expected Net Unpaid Loss</v>
       </c>
       <c r="C56">
-        <v>NaN</v>
+        <v>13940218</v>
       </c>
       <c r="D56">
-        <v>NaN</v>
+        <v>15243348</v>
       </c>
       <c r="E56">
-        <v>NaN</v>
+        <v>13602450</v>
       </c>
     </row>
     <row r="57">
@@ -4441,16 +4373,16 @@
         <v>Reserves</v>
       </c>
       <c r="B57" t="str">
-        <v>Ending RI Recoverable</v>
+        <v>Indicated Net Reserve at Confidence</v>
       </c>
       <c r="C57">
-        <v>NaN</v>
+        <v>18763533</v>
       </c>
       <c r="D57">
-        <v>NaN</v>
+        <v>20517547</v>
       </c>
       <c r="E57">
-        <v>NaN</v>
+        <v>18308897</v>
       </c>
     </row>
     <row r="58">
@@ -4458,50 +4390,50 @@
         <v>Reserves</v>
       </c>
       <c r="B58" t="str">
-        <v>Expected Net Unpaid Loss</v>
+        <v>Reserve Risk Margin Needed</v>
       </c>
       <c r="C58">
-        <v>13940218</v>
+        <v>13257147</v>
       </c>
       <c r="D58">
-        <v>15243348</v>
+        <v>14496424</v>
       </c>
       <c r="E58">
-        <v>13602450</v>
+        <v>12935930</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Reserves</v>
+        <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B59" t="str">
-        <v>Indicated Net Reserve at Confidence</v>
+        <v>Beginning Cash</v>
       </c>
       <c r="C59">
-        <v>18763533</v>
+        <v>2639238</v>
       </c>
       <c r="D59">
-        <v>20517547</v>
+        <v>2855708</v>
       </c>
       <c r="E59">
-        <v>18308897</v>
+        <v>3088953</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Reserves</v>
+        <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B60" t="str">
-        <v>Reserve Risk Margin Needed</v>
+        <v>Ending Cash</v>
       </c>
       <c r="C60">
-        <v>13257147</v>
+        <v>2856111</v>
       </c>
       <c r="D60">
-        <v>14496424</v>
+        <v>3088486</v>
       </c>
       <c r="E60">
-        <v>12935930</v>
+        <v>3216701</v>
       </c>
     </row>
     <row r="61">
@@ -4509,16 +4441,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B61" t="str">
-        <v>Beginning Cash</v>
+        <v>Beginning Investments</v>
       </c>
       <c r="C61">
-        <v>2639238</v>
+        <v>21604649</v>
       </c>
       <c r="D61">
-        <v>2855708</v>
+        <v>25508445</v>
       </c>
       <c r="E61">
-        <v>3088953</v>
+        <v>32716430</v>
       </c>
     </row>
     <row r="62">
@@ -4526,16 +4458,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B62" t="str">
-        <v>Ending Cash</v>
+        <v>Ending Investments</v>
       </c>
       <c r="C62">
-        <v>2856111</v>
+        <v>25508445</v>
       </c>
       <c r="D62">
-        <v>3088486</v>
+        <v>32716430</v>
       </c>
       <c r="E62">
-        <v>3216701</v>
+        <v>41111134</v>
       </c>
     </row>
     <row r="63">
@@ -4543,16 +4475,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B63" t="str">
-        <v>Beginning Investments</v>
+        <v>Other Assets</v>
       </c>
       <c r="C63">
-        <v>21604649</v>
+        <v>335834</v>
       </c>
       <c r="D63">
-        <v>25508445</v>
+        <v>328882</v>
       </c>
       <c r="E63">
-        <v>32716430</v>
+        <v>336919</v>
       </c>
     </row>
     <row r="64">
@@ -4560,16 +4492,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B64" t="str">
-        <v>Ending Investments</v>
+        <v>Total Assets</v>
       </c>
       <c r="C64">
-        <v>25508445</v>
+        <v>28700390</v>
       </c>
       <c r="D64">
-        <v>32716430</v>
+        <v>36133799</v>
       </c>
       <c r="E64">
-        <v>41111134</v>
+        <v>44664754</v>
       </c>
     </row>
     <row r="65">
@@ -4577,16 +4509,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B65" t="str">
-        <v>Other Assets</v>
+        <v>Unearned Premium</v>
       </c>
       <c r="C65">
-        <v>335834</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>328882</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>336919</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4594,16 +4526,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B66" t="str">
-        <v>Total Assets</v>
+        <v>Other Liabilities</v>
       </c>
       <c r="C66">
-        <v>28700390</v>
+        <v>355342</v>
       </c>
       <c r="D66">
-        <v>36133799</v>
+        <v>347986</v>
       </c>
       <c r="E66">
-        <v>44664754</v>
+        <v>356490</v>
       </c>
     </row>
     <row r="67">
@@ -4611,16 +4543,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B67" t="str">
-        <v>Unearned Premium</v>
+        <v>Total Liabilities</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>14295559</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>15591334</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>13958940</v>
       </c>
     </row>
     <row r="68">
@@ -4628,16 +4560,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B68" t="str">
-        <v>Other Liabilities</v>
+        <v>Beginning Surplus</v>
       </c>
       <c r="C68">
-        <v>355342</v>
+        <v>14776660</v>
       </c>
       <c r="D68">
-        <v>347986</v>
+        <v>14404831</v>
       </c>
       <c r="E68">
-        <v>356490</v>
+        <v>20542465</v>
       </c>
     </row>
     <row r="69">
@@ -4645,16 +4577,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B69" t="str">
-        <v>Total Liabilities</v>
+        <v>Surplus from Income</v>
       </c>
       <c r="C69">
-        <v>14295559</v>
+        <v>14404831</v>
       </c>
       <c r="D69">
-        <v>15591334</v>
+        <v>20542465</v>
       </c>
       <c r="E69">
-        <v>13958940</v>
+        <v>30705814</v>
       </c>
     </row>
     <row r="70">
@@ -4662,16 +4594,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B70" t="str">
-        <v>Beginning Surplus</v>
+        <v>Ending Surplus</v>
       </c>
       <c r="C70">
-        <v>14776660</v>
+        <v>14404831</v>
       </c>
       <c r="D70">
-        <v>14404831</v>
+        <v>20542465</v>
       </c>
       <c r="E70">
-        <v>20542465</v>
+        <v>30705814</v>
       </c>
     </row>
     <row r="71">
@@ -4679,41 +4611,41 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B71" t="str">
-        <v>Surplus from Income</v>
+        <v>Surplus Tie-Out Difference</v>
       </c>
       <c r="C71">
-        <v>14404831</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>20542465</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>30705814</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Balance Sheet and Surplus</v>
+        <v>Inter-Line Loan</v>
       </c>
       <c r="B72" t="str">
-        <v>Ending Surplus</v>
+        <v>Loan Originated This Year</v>
       </c>
       <c r="C72">
-        <v>14404831</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>20542465</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>30705814</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Balance Sheet and Surplus</v>
+        <v>Inter-Line Loan</v>
       </c>
       <c r="B73" t="str">
-        <v>Surplus Tie-Out Difference</v>
+        <v>Loan Interest Accrued</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -4730,7 +4662,7 @@
         <v>Inter-Line Loan</v>
       </c>
       <c r="B74" t="str">
-        <v>Loan Originated This Year</v>
+        <v>Loan Repayment Applied</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -4747,7 +4679,7 @@
         <v>Inter-Line Loan</v>
       </c>
       <c r="B75" t="str">
-        <v>Loan Interest Accrued</v>
+        <v>Outstanding Loan Balance</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -4761,36 +4693,36 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Inter-Line Loan</v>
+        <v>Ratios and Capital</v>
       </c>
       <c r="B76" t="str">
-        <v>Loan Repayment Applied</v>
+        <v>Expected Loss Ratio</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>0.6684491978609625</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>0.6684491978609626</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>0.6684491978609626</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Inter-Line Loan</v>
+        <v>Ratios and Capital</v>
       </c>
       <c r="B77" t="str">
-        <v>Outstanding Loan Balance</v>
+        <v>Expected Expense Ratio</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>0.33155080213903754</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>0.3315508021390374</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>0.3315508021390374</v>
       </c>
     </row>
     <row r="78">
@@ -4798,16 +4730,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B78" t="str">
-        <v>Expected Loss Ratio</v>
+        <v>Expected Combined Ratio</v>
       </c>
       <c r="C78">
-        <v>0.6684491978609625</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>0.6684491978609626</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>0.6684491978609626</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4815,16 +4747,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B79" t="str">
-        <v>Expected Expense Ratio</v>
+        <v>Actual Loss Ratio</v>
       </c>
       <c r="C79">
-        <v>0.33155080213903754</v>
+        <v>0.6808088080275256</v>
       </c>
       <c r="D79">
-        <v>0.3315508021390374</v>
+        <v>0.4997805801598653</v>
       </c>
       <c r="E79">
-        <v>0.3315508021390374</v>
+        <v>0.2863141043778507</v>
       </c>
     </row>
     <row r="80">
@@ -4832,16 +4764,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B80" t="str">
-        <v>Expected Combined Ratio</v>
+        <v>Actual Expense Ratio</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>0.3294687740591458</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0.3294687740591458</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>0.3294687740591459</v>
       </c>
     </row>
     <row r="81">
@@ -4849,16 +4781,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B81" t="str">
-        <v>Actual Loss Ratio</v>
+        <v>Actual Combined Ratio</v>
       </c>
       <c r="C81">
-        <v>0.6808088080275256</v>
+        <v>1.0102775820866714</v>
       </c>
       <c r="D81">
-        <v>0.4997805801598653</v>
+        <v>0.8292493542190111</v>
       </c>
       <c r="E81">
-        <v>0.2863141043778507</v>
+        <v>0.6157828784369965</v>
       </c>
     </row>
     <row r="82">
@@ -4866,16 +4798,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B82" t="str">
-        <v>Actual Expense Ratio</v>
+        <v>Surplus</v>
       </c>
       <c r="C82">
-        <v>0.3294687740591458</v>
+        <v>14404831</v>
       </c>
       <c r="D82">
-        <v>0.3294687740591458</v>
+        <v>20542465</v>
       </c>
       <c r="E82">
-        <v>0.3294687740591459</v>
+        <v>30705814</v>
       </c>
     </row>
     <row r="83">
@@ -4883,16 +4815,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B83" t="str">
-        <v>Actual Combined Ratio</v>
+        <v>Excess Available Surplus</v>
       </c>
       <c r="C83">
-        <v>1.0102775820866714</v>
+        <v>1147684</v>
       </c>
       <c r="D83">
-        <v>0.8292493542190111</v>
+        <v>6046040</v>
       </c>
       <c r="E83">
-        <v>0.6157828784369965</v>
+        <v>17769884</v>
       </c>
     </row>
     <row r="84">
@@ -4900,16 +4832,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B84" t="str">
-        <v>Surplus</v>
+        <v>Excess Capital Ratio</v>
       </c>
       <c r="C84">
-        <v>14404831</v>
+        <v>0.08657097262107852</v>
       </c>
       <c r="D84">
-        <v>20542465</v>
+        <v>0.4170711482900847</v>
       </c>
       <c r="E84">
-        <v>30705814</v>
+        <v>1.3736843849859297</v>
       </c>
     </row>
     <row r="85">
@@ -4917,62 +4849,28 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B85" t="str">
-        <v>Excess Available Surplus</v>
-      </c>
-      <c r="C85">
-        <v>1147684</v>
-      </c>
-      <c r="D85">
-        <v>6046040</v>
-      </c>
-      <c r="E85">
-        <v>17769884</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Excess Capital Ratio</v>
-      </c>
-      <c r="C86">
-        <v>0.08657097262107852</v>
-      </c>
-      <c r="D86">
-        <v>0.4170711482900847</v>
-      </c>
-      <c r="E86">
-        <v>1.3736843849859297</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B87" t="str">
         <v>Excess Capital Status</v>
       </c>
-      <c r="C87" t="str">
+      <c r="C85" t="str">
         <v>Adequate</v>
       </c>
-      <c r="D87" t="str">
+      <c r="D85" t="str">
         <v>Strong</v>
       </c>
-      <c r="E87" t="str">
+      <c r="E85" t="str">
         <v>Strong</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E85"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E85"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5846,16 +5744,16 @@
         <v>Reserves</v>
       </c>
       <c r="B52" t="str">
-        <v>Beginning Gross Reserve</v>
+        <v>Beginning Net Reserve</v>
       </c>
       <c r="C52">
-        <v>NaN</v>
+        <v>3139762</v>
       </c>
       <c r="D52">
-        <v>NaN</v>
+        <v>2882046</v>
       </c>
       <c r="E52">
-        <v>NaN</v>
+        <v>3609435</v>
       </c>
     </row>
     <row r="53">
@@ -5863,16 +5761,16 @@
         <v>Reserves</v>
       </c>
       <c r="B53" t="str">
-        <v>Current-Year Gross Reserve</v>
+        <v>Current-Year Net Reserve</v>
       </c>
       <c r="C53">
-        <v>NaN</v>
+        <v>1806732</v>
       </c>
       <c r="D53">
-        <v>NaN</v>
+        <v>2583181</v>
       </c>
       <c r="E53">
-        <v>NaN</v>
+        <v>2084278</v>
       </c>
     </row>
     <row r="54">
@@ -5880,16 +5778,16 @@
         <v>Reserves</v>
       </c>
       <c r="B54" t="str">
-        <v>Gross Paid Losses</v>
+        <v>Net Paid Losses</v>
       </c>
       <c r="C54">
-        <v>NaN</v>
+        <v>3201500</v>
       </c>
       <c r="D54">
-        <v>NaN</v>
+        <v>3628021</v>
       </c>
       <c r="E54">
-        <v>NaN</v>
+        <v>3819312</v>
       </c>
     </row>
     <row r="55">
@@ -5897,16 +5795,16 @@
         <v>Reserves</v>
       </c>
       <c r="B55" t="str">
-        <v>Ending Gross Reserve</v>
+        <v>Ending Net Reserve</v>
       </c>
       <c r="C55">
-        <v>NaN</v>
+        <v>2882046</v>
       </c>
       <c r="D55">
-        <v>NaN</v>
+        <v>3609435</v>
       </c>
       <c r="E55">
-        <v>NaN</v>
+        <v>3392629</v>
       </c>
     </row>
     <row r="56">
@@ -5914,16 +5812,16 @@
         <v>Reserves</v>
       </c>
       <c r="B56" t="str">
-        <v>Beginning RI Recoverable</v>
+        <v>Expected Net Unpaid Loss</v>
       </c>
       <c r="C56">
-        <v>NaN</v>
+        <v>2882046</v>
       </c>
       <c r="D56">
-        <v>NaN</v>
+        <v>3609435</v>
       </c>
       <c r="E56">
-        <v>NaN</v>
+        <v>3392629</v>
       </c>
     </row>
     <row r="57">
@@ -5931,16 +5829,16 @@
         <v>Reserves</v>
       </c>
       <c r="B57" t="str">
-        <v>Ending RI Recoverable</v>
+        <v>Indicated Net Reserve at Confidence</v>
       </c>
       <c r="C57">
-        <v>NaN</v>
+        <v>3879234</v>
       </c>
       <c r="D57">
-        <v>NaN</v>
+        <v>4858299</v>
       </c>
       <c r="E57">
-        <v>NaN</v>
+        <v>4566478</v>
       </c>
     </row>
     <row r="58">
@@ -5948,50 +5846,50 @@
         <v>Reserves</v>
       </c>
       <c r="B58" t="str">
-        <v>Expected Net Unpaid Loss</v>
+        <v>Reserve Risk Margin Needed</v>
       </c>
       <c r="C58">
-        <v>2882046</v>
+        <v>2740826</v>
       </c>
       <c r="D58">
-        <v>3609435</v>
+        <v>3432572</v>
       </c>
       <c r="E58">
-        <v>3392629</v>
+        <v>3226390</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Reserves</v>
+        <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B59" t="str">
-        <v>Indicated Net Reserve at Confidence</v>
+        <v>Beginning Cash</v>
       </c>
       <c r="C59">
-        <v>3879234</v>
+        <v>1156737</v>
       </c>
       <c r="D59">
-        <v>4858299</v>
+        <v>1391776</v>
       </c>
       <c r="E59">
-        <v>4566478</v>
+        <v>1508155</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Reserves</v>
+        <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B60" t="str">
-        <v>Reserve Risk Margin Needed</v>
+        <v>Ending Cash</v>
       </c>
       <c r="C60">
-        <v>2740826</v>
+        <v>1391016</v>
       </c>
       <c r="D60">
-        <v>3432572</v>
+        <v>1507910</v>
       </c>
       <c r="E60">
-        <v>3226390</v>
+        <v>1467821</v>
       </c>
     </row>
     <row r="61">
@@ -5999,16 +5897,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B61" t="str">
-        <v>Beginning Cash</v>
+        <v>Beginning Investments</v>
       </c>
       <c r="C61">
-        <v>1156737</v>
+        <v>9670980</v>
       </c>
       <c r="D61">
-        <v>1391776</v>
+        <v>12374487</v>
       </c>
       <c r="E61">
-        <v>1508155</v>
+        <v>16642921</v>
       </c>
     </row>
     <row r="62">
@@ -6016,16 +5914,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B62" t="str">
-        <v>Ending Cash</v>
+        <v>Ending Investments</v>
       </c>
       <c r="C62">
-        <v>1391016</v>
+        <v>12374487</v>
       </c>
       <c r="D62">
-        <v>1507910</v>
+        <v>16642921</v>
       </c>
       <c r="E62">
-        <v>1467821</v>
+        <v>20404120</v>
       </c>
     </row>
     <row r="63">
@@ -6033,16 +5931,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B63" t="str">
-        <v>Beginning Investments</v>
+        <v>Other Assets</v>
       </c>
       <c r="C63">
-        <v>9670980</v>
+        <v>147191</v>
       </c>
       <c r="D63">
-        <v>12374487</v>
+        <v>160286</v>
       </c>
       <c r="E63">
-        <v>16642921</v>
+        <v>164498</v>
       </c>
     </row>
     <row r="64">
@@ -6050,16 +5948,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B64" t="str">
-        <v>Ending Investments</v>
+        <v>Total Assets</v>
       </c>
       <c r="C64">
-        <v>12374487</v>
+        <v>13912693</v>
       </c>
       <c r="D64">
-        <v>16642921</v>
+        <v>18311117</v>
       </c>
       <c r="E64">
-        <v>20404120</v>
+        <v>22036439</v>
       </c>
     </row>
     <row r="65">
@@ -6067,16 +5965,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B65" t="str">
-        <v>Other Assets</v>
+        <v>Unearned Premium</v>
       </c>
       <c r="C65">
-        <v>147191</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>160286</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>164498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -6084,16 +5982,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B66" t="str">
-        <v>Total Assets</v>
+        <v>Other Liabilities</v>
       </c>
       <c r="C66">
-        <v>13912693</v>
+        <v>155741</v>
       </c>
       <c r="D66">
-        <v>18311117</v>
+        <v>169597</v>
       </c>
       <c r="E66">
-        <v>22036439</v>
+        <v>174053</v>
       </c>
     </row>
     <row r="67">
@@ -6101,16 +5999,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B67" t="str">
-        <v>Unearned Premium</v>
+        <v>Total Liabilities</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>3037787</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>3779031</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>3566682</v>
       </c>
     </row>
     <row r="68">
@@ -6118,16 +6016,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B68" t="str">
-        <v>Other Liabilities</v>
+        <v>Beginning Surplus</v>
       </c>
       <c r="C68">
-        <v>155741</v>
+        <v>7679406</v>
       </c>
       <c r="D68">
-        <v>169597</v>
+        <v>10874906</v>
       </c>
       <c r="E68">
-        <v>174053</v>
+        <v>14532086</v>
       </c>
     </row>
     <row r="69">
@@ -6135,16 +6033,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B69" t="str">
-        <v>Total Liabilities</v>
+        <v>Surplus from Income</v>
       </c>
       <c r="C69">
-        <v>3037787</v>
+        <v>10874906</v>
       </c>
       <c r="D69">
-        <v>3779031</v>
+        <v>14532086</v>
       </c>
       <c r="E69">
-        <v>3566682</v>
+        <v>18469757</v>
       </c>
     </row>
     <row r="70">
@@ -6152,16 +6050,16 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B70" t="str">
-        <v>Beginning Surplus</v>
+        <v>Ending Surplus</v>
       </c>
       <c r="C70">
-        <v>7679406</v>
+        <v>10874906</v>
       </c>
       <c r="D70">
-        <v>10874906</v>
+        <v>14532086</v>
       </c>
       <c r="E70">
-        <v>14532086</v>
+        <v>18469757</v>
       </c>
     </row>
     <row r="71">
@@ -6169,41 +6067,41 @@
         <v>Balance Sheet and Surplus</v>
       </c>
       <c r="B71" t="str">
-        <v>Surplus from Income</v>
+        <v>Surplus Tie-Out Difference</v>
       </c>
       <c r="C71">
-        <v>10874906</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>14532086</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>18469757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Balance Sheet and Surplus</v>
+        <v>Inter-Line Loan</v>
       </c>
       <c r="B72" t="str">
-        <v>Ending Surplus</v>
+        <v>Loan Originated This Year</v>
       </c>
       <c r="C72">
-        <v>10874906</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>14532086</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>18469757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Balance Sheet and Surplus</v>
+        <v>Inter-Line Loan</v>
       </c>
       <c r="B73" t="str">
-        <v>Surplus Tie-Out Difference</v>
+        <v>Loan Interest Accrued</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -6220,7 +6118,7 @@
         <v>Inter-Line Loan</v>
       </c>
       <c r="B74" t="str">
-        <v>Loan Originated This Year</v>
+        <v>Loan Repayment Applied</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -6237,7 +6135,7 @@
         <v>Inter-Line Loan</v>
       </c>
       <c r="B75" t="str">
-        <v>Loan Interest Accrued</v>
+        <v>Outstanding Loan Balance</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -6251,36 +6149,36 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Inter-Line Loan</v>
+        <v>Ratios and Capital</v>
       </c>
       <c r="B76" t="str">
-        <v>Loan Repayment Applied</v>
+        <v>Expected Loss Ratio</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>0.6684491978609626</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>0.6684491978609624</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>0.6684491978609625</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Inter-Line Loan</v>
+        <v>Ratios and Capital</v>
       </c>
       <c r="B77" t="str">
-        <v>Outstanding Loan Balance</v>
+        <v>Expected Expense Ratio</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>0.3315508021390374</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>0.33155080213903765</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>0.33155080213903754</v>
       </c>
     </row>
     <row r="78">
@@ -6288,16 +6186,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B78" t="str">
-        <v>Expected Loss Ratio</v>
+        <v>Expected Combined Ratio</v>
       </c>
       <c r="C78">
-        <v>0.6684491978609626</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>0.6684491978609624</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>0.6684491978609625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -6305,16 +6203,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B79" t="str">
-        <v>Expected Expense Ratio</v>
+        <v>Actual Loss Ratio</v>
       </c>
       <c r="C79">
-        <v>0.3315508021390374</v>
+        <v>0.3174426326741114</v>
       </c>
       <c r="D79">
-        <v>0.33155080213903765</v>
+        <v>0.4332561106770481</v>
       </c>
       <c r="E79">
-        <v>0.33155080213903754</v>
+        <v>0.36814839315598347</v>
       </c>
     </row>
     <row r="80">
@@ -6322,16 +6220,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B80" t="str">
-        <v>Expected Combined Ratio</v>
+        <v>Actual Expense Ratio</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>0.3294687740591459</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0.3294687740591459</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>0.3294687740591459</v>
       </c>
     </row>
     <row r="81">
@@ -6339,16 +6237,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B81" t="str">
-        <v>Actual Loss Ratio</v>
+        <v>Actual Combined Ratio</v>
       </c>
       <c r="C81">
-        <v>0.3174426326741114</v>
+        <v>0.6469114067332573</v>
       </c>
       <c r="D81">
-        <v>0.4332561106770481</v>
+        <v>0.762724884736194</v>
       </c>
       <c r="E81">
-        <v>0.36814839315598347</v>
+        <v>0.6976171672151293</v>
       </c>
     </row>
     <row r="82">
@@ -6356,16 +6254,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B82" t="str">
-        <v>Actual Expense Ratio</v>
+        <v>Surplus</v>
       </c>
       <c r="C82">
-        <v>0.3294687740591459</v>
+        <v>10874906</v>
       </c>
       <c r="D82">
-        <v>0.3294687740591459</v>
+        <v>14532086</v>
       </c>
       <c r="E82">
-        <v>0.3294687740591459</v>
+        <v>18469757</v>
       </c>
     </row>
     <row r="83">
@@ -6373,16 +6271,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B83" t="str">
-        <v>Actual Combined Ratio</v>
+        <v>Excess Available Surplus</v>
       </c>
       <c r="C83">
-        <v>0.6469114067332573</v>
+        <v>8134080</v>
       </c>
       <c r="D83">
-        <v>0.762724884736194</v>
+        <v>11099513</v>
       </c>
       <c r="E83">
-        <v>0.6976171672151293</v>
+        <v>15243367</v>
       </c>
     </row>
     <row r="84">
@@ -6390,16 +6288,16 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B84" t="str">
-        <v>Surplus</v>
+        <v>Excess Capital Ratio</v>
       </c>
       <c r="C84">
-        <v>10874906</v>
+        <v>2.9677480659323296</v>
       </c>
       <c r="D84">
-        <v>14532086</v>
+        <v>3.2335845186780525</v>
       </c>
       <c r="E84">
-        <v>18469757</v>
+        <v>4.724589326199767</v>
       </c>
     </row>
     <row r="85">
@@ -6407,55 +6305,21 @@
         <v>Ratios and Capital</v>
       </c>
       <c r="B85" t="str">
-        <v>Excess Available Surplus</v>
-      </c>
-      <c r="C85">
-        <v>8134080</v>
-      </c>
-      <c r="D85">
-        <v>11099513</v>
-      </c>
-      <c r="E85">
-        <v>15243367</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Excess Capital Ratio</v>
-      </c>
-      <c r="C86">
-        <v>2.9677480659323296</v>
-      </c>
-      <c r="D86">
-        <v>3.2335845186780525</v>
-      </c>
-      <c r="E86">
-        <v>4.724589326199767</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>Ratios and Capital</v>
-      </c>
-      <c r="B87" t="str">
         <v>Excess Capital Status</v>
       </c>
-      <c r="C87" t="str">
+      <c r="C85" t="str">
         <v>Strong</v>
       </c>
-      <c r="D87" t="str">
+      <c r="D85" t="str">
         <v>Strong</v>
       </c>
-      <c r="E87" t="str">
+      <c r="E85" t="str">
         <v>Strong</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E85"/>
   </ignoredErrors>
 </worksheet>
 </file>